--- a/monet/tests/TestData/calibrate/pwrmeasured_561nm.xlsx
+++ b/monet/tests/TestData/calibrate/pwrmeasured_561nm.xlsx
@@ -444,13 +444,13 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>127.7081837141911</v>
+        <v>128.1316944839602</v>
       </c>
       <c r="C2" t="n">
-        <v>4.641147026181587</v>
+        <v>5.94708543263482</v>
       </c>
       <c r="D2" t="n">
-        <v>361.6216909649959</v>
+        <v>355.6323106243711</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>35</v>
       </c>
       <c r="B3" t="n">
-        <v>200.7386088543682</v>
+        <v>202.7990947086088</v>
       </c>
       <c r="C3" t="n">
-        <v>64.41870741250227</v>
+        <v>66.3820485251301</v>
       </c>
       <c r="D3" t="n">
-        <v>136.739347519481</v>
+        <v>133.6645497952943</v>
       </c>
     </row>
     <row r="4">
@@ -472,13 +472,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="n">
-        <v>264.5105786363305</v>
+        <v>273.5656457887301</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5894019875104</v>
+        <v>176.1588214135698</v>
       </c>
       <c r="D4" t="n">
-        <v>13.9048090161781</v>
+        <v>14.40176149527618</v>
       </c>
     </row>
     <row r="5">
@@ -486,13 +486,13 @@
         <v>45</v>
       </c>
       <c r="B5" t="n">
-        <v>325.9948012477694</v>
+        <v>327.2502048416414</v>
       </c>
       <c r="C5" t="n">
-        <v>332.0002693126586</v>
+        <v>332.7466676627761</v>
       </c>
       <c r="D5" t="n">
-        <v>9.437805600287268</v>
+        <v>19.77014722132325</v>
       </c>
     </row>
     <row r="6">
@@ -500,13 +500,13 @@
         <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>368.0623632553033</v>
+        <v>370.3982828500636</v>
       </c>
       <c r="C6" t="n">
-        <v>501.1668888283496</v>
+        <v>495.9930623168193</v>
       </c>
       <c r="D6" t="n">
-        <v>131.553295705596</v>
+        <v>139.7803913844442</v>
       </c>
     </row>
     <row r="7">
@@ -514,13 +514,13 @@
         <v>55</v>
       </c>
       <c r="B7" t="n">
-        <v>392.8711411040526</v>
+        <v>399.4156166670818</v>
       </c>
       <c r="C7" t="n">
-        <v>672.4491575089664</v>
+        <v>673.7545050745493</v>
       </c>
       <c r="D7" t="n">
-        <v>354.8121494734247</v>
+        <v>357.7902037072269</v>
       </c>
     </row>
     <row r="8">
@@ -528,13 +528,13 @@
         <v>60</v>
       </c>
       <c r="B8" t="n">
-        <v>395.7157778883991</v>
+        <v>395.8165388784107</v>
       </c>
       <c r="C8" t="n">
-        <v>820.9124227616545</v>
+        <v>819.1239160367136</v>
       </c>
       <c r="D8" t="n">
-        <v>658.6651932340776</v>
+        <v>660.2870453686517</v>
       </c>
     </row>
     <row r="9">
@@ -542,13 +542,13 @@
         <v>65</v>
       </c>
       <c r="B9" t="n">
-        <v>366.3963219726277</v>
+        <v>369.6942327879953</v>
       </c>
       <c r="C9" t="n">
-        <v>930.4281802205659</v>
+        <v>931.6266607182259</v>
       </c>
       <c r="D9" t="n">
-        <v>998.9153281288075</v>
+        <v>994.7617031978539</v>
       </c>
     </row>
     <row r="10">
@@ -556,13 +556,13 @@
         <v>70</v>
       </c>
       <c r="B10" t="n">
-        <v>326.4103666146893</v>
+        <v>327.5481561154608</v>
       </c>
       <c r="C10" t="n">
-        <v>994.0104160250976</v>
+        <v>992.9197853901032</v>
       </c>
       <c r="D10" t="n">
-        <v>1340.778411760881</v>
+        <v>1339.07327752161</v>
       </c>
     </row>
     <row r="11">
@@ -570,13 +570,13 @@
         <v>75</v>
       </c>
       <c r="B11" t="n">
-        <v>271.6307271567391</v>
+        <v>269.5666439641561</v>
       </c>
       <c r="C11" t="n">
-        <v>995.3336400348576</v>
+        <v>993.5110113983064</v>
       </c>
       <c r="D11" t="n">
-        <v>1642.597788042258</v>
+        <v>1642.351299091653</v>
       </c>
     </row>
     <row r="12">
@@ -584,13 +584,13 @@
         <v>80</v>
       </c>
       <c r="B12" t="n">
-        <v>203.3262251811043</v>
+        <v>200.7897884707143</v>
       </c>
       <c r="C12" t="n">
-        <v>932.5508514715801</v>
+        <v>938.5234633348789</v>
       </c>
       <c r="D12" t="n">
-        <v>1867.740733694181</v>
+        <v>1866.568792517432</v>
       </c>
     </row>
     <row r="13">
@@ -598,13 +598,13 @@
         <v>85</v>
       </c>
       <c r="B13" t="n">
-        <v>133.1837276402744</v>
+        <v>131.2020624645072</v>
       </c>
       <c r="C13" t="n">
-        <v>823.6003861437745</v>
+        <v>824.7209545090136</v>
       </c>
       <c r="D13" t="n">
-        <v>1983.697819799075</v>
+        <v>1984.48861755012</v>
       </c>
     </row>
     <row r="14">
@@ -612,13 +612,13 @@
         <v>90</v>
       </c>
       <c r="B14" t="n">
-        <v>76.09689261971261</v>
+        <v>73.60002929758311</v>
       </c>
       <c r="C14" t="n">
-        <v>674.5646262594684</v>
+        <v>671.0641224646456</v>
       </c>
       <c r="D14" t="n">
-        <v>1982.216334035904</v>
+        <v>1979.655597315004</v>
       </c>
     </row>
     <row r="15">
@@ -626,13 +626,13 @@
         <v>95</v>
       </c>
       <c r="B15" t="n">
-        <v>29.24775354459174</v>
+        <v>25.20211531660541</v>
       </c>
       <c r="C15" t="n">
-        <v>498.8389739912111</v>
+        <v>501.14705533248</v>
       </c>
       <c r="D15" t="n">
-        <v>1864.77379878872</v>
+        <v>1865.292279613888</v>
       </c>
     </row>
     <row r="16">
@@ -640,13 +640,13 @@
         <v>100</v>
       </c>
       <c r="B16" t="n">
-        <v>-2.660906480795135</v>
+        <v>0.686827941337449</v>
       </c>
       <c r="C16" t="n">
-        <v>329.412843616884</v>
+        <v>330.8733458476201</v>
       </c>
       <c r="D16" t="n">
-        <v>1644.350057426763</v>
+        <v>1642.687694091989</v>
       </c>
     </row>
   </sheetData>

--- a/monet/tests/TestData/calibrate/pwrmeasured_561nm.xlsx
+++ b/monet/tests/TestData/calibrate/pwrmeasured_561nm.xlsx
@@ -444,13 +444,13 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>128.1316944839602</v>
+        <v>131.1507695605644</v>
       </c>
       <c r="C2" t="n">
-        <v>5.94708543263482</v>
+        <v>8.329088310128897</v>
       </c>
       <c r="D2" t="n">
-        <v>355.6323106243711</v>
+        <v>355.3771028751793</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>35</v>
       </c>
       <c r="B3" t="n">
-        <v>202.7990947086088</v>
+        <v>204.7047850043625</v>
       </c>
       <c r="C3" t="n">
-        <v>66.3820485251301</v>
+        <v>61.61277707416036</v>
       </c>
       <c r="D3" t="n">
-        <v>133.6645497952943</v>
+        <v>131.6775316754557</v>
       </c>
     </row>
     <row r="4">
@@ -472,13 +472,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="n">
-        <v>273.5656457887301</v>
+        <v>266.196554220388</v>
       </c>
       <c r="C4" t="n">
-        <v>176.1588214135698</v>
+        <v>176.5936958497256</v>
       </c>
       <c r="D4" t="n">
-        <v>14.40176149527618</v>
+        <v>9.996410076189544</v>
       </c>
     </row>
     <row r="5">
@@ -486,13 +486,13 @@
         <v>45</v>
       </c>
       <c r="B5" t="n">
-        <v>327.2502048416414</v>
+        <v>328.9321783260638</v>
       </c>
       <c r="C5" t="n">
-        <v>332.7466676627761</v>
+        <v>329.5797937277267</v>
       </c>
       <c r="D5" t="n">
-        <v>19.77014722132325</v>
+        <v>23.10382135563498</v>
       </c>
     </row>
     <row r="6">
@@ -500,13 +500,13 @@
         <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>370.3982828500636</v>
+        <v>376.3100401079016</v>
       </c>
       <c r="C6" t="n">
-        <v>495.9930623168193</v>
+        <v>496.7932471441222</v>
       </c>
       <c r="D6" t="n">
-        <v>139.7803913844442</v>
+        <v>132.4510077838675</v>
       </c>
     </row>
     <row r="7">
@@ -514,13 +514,13 @@
         <v>55</v>
       </c>
       <c r="B7" t="n">
-        <v>399.4156166670818</v>
+        <v>394.4563564248913</v>
       </c>
       <c r="C7" t="n">
-        <v>673.7545050745493</v>
+        <v>672.5589995168162</v>
       </c>
       <c r="D7" t="n">
-        <v>357.7902037072269</v>
+        <v>351.9371478376641</v>
       </c>
     </row>
     <row r="8">
@@ -528,13 +528,13 @@
         <v>60</v>
       </c>
       <c r="B8" t="n">
-        <v>395.8165388784107</v>
+        <v>397.0350922179805</v>
       </c>
       <c r="C8" t="n">
-        <v>819.1239160367136</v>
+        <v>825.3543083202798</v>
       </c>
       <c r="D8" t="n">
-        <v>660.2870453686517</v>
+        <v>656.239965458995</v>
       </c>
     </row>
     <row r="9">
@@ -542,13 +542,13 @@
         <v>65</v>
       </c>
       <c r="B9" t="n">
-        <v>369.6942327879953</v>
+        <v>379.3979856054268</v>
       </c>
       <c r="C9" t="n">
-        <v>931.6266607182259</v>
+        <v>932.9747984626913</v>
       </c>
       <c r="D9" t="n">
-        <v>994.7617031978539</v>
+        <v>1005.457023901773</v>
       </c>
     </row>
     <row r="10">
@@ -556,13 +556,13 @@
         <v>70</v>
       </c>
       <c r="B10" t="n">
-        <v>327.5481561154608</v>
+        <v>325.6494752352597</v>
       </c>
       <c r="C10" t="n">
-        <v>992.9197853901032</v>
+        <v>989.6748528158339</v>
       </c>
       <c r="D10" t="n">
-        <v>1339.07327752161</v>
+        <v>1341.45392263164</v>
       </c>
     </row>
     <row r="11">
@@ -570,13 +570,13 @@
         <v>75</v>
       </c>
       <c r="B11" t="n">
-        <v>269.5666439641561</v>
+        <v>267.3840744768929</v>
       </c>
       <c r="C11" t="n">
-        <v>993.5110113983064</v>
+        <v>991.3869797313644</v>
       </c>
       <c r="D11" t="n">
-        <v>1642.351299091653</v>
+        <v>1643.660872689891</v>
       </c>
     </row>
     <row r="12">
@@ -584,13 +584,13 @@
         <v>80</v>
       </c>
       <c r="B12" t="n">
-        <v>200.7897884707143</v>
+        <v>205.4718866429973</v>
       </c>
       <c r="C12" t="n">
-        <v>938.5234633348789</v>
+        <v>932.816019498408</v>
       </c>
       <c r="D12" t="n">
-        <v>1866.568792517432</v>
+        <v>1868.691502717583</v>
       </c>
     </row>
     <row r="13">
@@ -598,13 +598,13 @@
         <v>85</v>
       </c>
       <c r="B13" t="n">
-        <v>131.2020624645072</v>
+        <v>132.4139451995842</v>
       </c>
       <c r="C13" t="n">
-        <v>824.7209545090136</v>
+        <v>822.4027002645677</v>
       </c>
       <c r="D13" t="n">
-        <v>1984.48861755012</v>
+        <v>1984.096132317718</v>
       </c>
     </row>
     <row r="14">
@@ -612,13 +612,13 @@
         <v>90</v>
       </c>
       <c r="B14" t="n">
-        <v>73.60002929758311</v>
+        <v>62.17260080309742</v>
       </c>
       <c r="C14" t="n">
-        <v>671.0641224646456</v>
+        <v>674.5025723399954</v>
       </c>
       <c r="D14" t="n">
-        <v>1979.655597315004</v>
+        <v>1983.882430329726</v>
       </c>
     </row>
     <row r="15">
@@ -626,13 +626,13 @@
         <v>95</v>
       </c>
       <c r="B15" t="n">
-        <v>25.20211531660541</v>
+        <v>23.62025291794367</v>
       </c>
       <c r="C15" t="n">
-        <v>501.14705533248</v>
+        <v>498.7096043652177</v>
       </c>
       <c r="D15" t="n">
-        <v>1865.292279613888</v>
+        <v>1871.543880786719</v>
       </c>
     </row>
     <row r="16">
@@ -640,13 +640,13 @@
         <v>100</v>
       </c>
       <c r="B16" t="n">
-        <v>0.686827941337449</v>
+        <v>4.002334974620731</v>
       </c>
       <c r="C16" t="n">
-        <v>330.8733458476201</v>
+        <v>338.4877288291863</v>
       </c>
       <c r="D16" t="n">
-        <v>1642.687694091989</v>
+        <v>1640.495898863647</v>
       </c>
     </row>
   </sheetData>

--- a/monet/tests/TestData/calibrate/pwrmeasured_561nm.xlsx
+++ b/monet/tests/TestData/calibrate/pwrmeasured_561nm.xlsx
@@ -444,13 +444,13 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>131.1507695605644</v>
+        <v>131.969111171953</v>
       </c>
       <c r="C2" t="n">
-        <v>8.329088310128897</v>
+        <v>5.94018157135772</v>
       </c>
       <c r="D2" t="n">
-        <v>355.3771028751793</v>
+        <v>359.1372415601662</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>35</v>
       </c>
       <c r="B3" t="n">
-        <v>204.7047850043625</v>
+        <v>193.8541630835422</v>
       </c>
       <c r="C3" t="n">
-        <v>61.61277707416036</v>
+        <v>61.99183246980382</v>
       </c>
       <c r="D3" t="n">
-        <v>131.6775316754557</v>
+        <v>135.6314905287634</v>
       </c>
     </row>
     <row r="4">
@@ -472,13 +472,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="n">
-        <v>266.196554220388</v>
+        <v>265.0945750643727</v>
       </c>
       <c r="C4" t="n">
-        <v>176.5936958497256</v>
+        <v>180.2728142273752</v>
       </c>
       <c r="D4" t="n">
-        <v>9.996410076189544</v>
+        <v>15.42443769546204</v>
       </c>
     </row>
     <row r="5">
@@ -486,13 +486,13 @@
         <v>45</v>
       </c>
       <c r="B5" t="n">
-        <v>328.9321783260638</v>
+        <v>325.1442447534625</v>
       </c>
       <c r="C5" t="n">
-        <v>329.5797937277267</v>
+        <v>331.0523127632416</v>
       </c>
       <c r="D5" t="n">
-        <v>23.10382135563498</v>
+        <v>19.9204713420517</v>
       </c>
     </row>
     <row r="6">
@@ -500,13 +500,13 @@
         <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>376.3100401079016</v>
+        <v>373.3555066495359</v>
       </c>
       <c r="C6" t="n">
-        <v>496.7932471441222</v>
+        <v>497.6593583395203</v>
       </c>
       <c r="D6" t="n">
-        <v>132.4510077838675</v>
+        <v>139.8394480500594</v>
       </c>
     </row>
     <row r="7">
@@ -514,13 +514,13 @@
         <v>55</v>
       </c>
       <c r="B7" t="n">
-        <v>394.4563564248913</v>
+        <v>395.3074264806115</v>
       </c>
       <c r="C7" t="n">
-        <v>672.5589995168162</v>
+        <v>672.5777769549796</v>
       </c>
       <c r="D7" t="n">
-        <v>351.9371478376641</v>
+        <v>357.2913190098304</v>
       </c>
     </row>
     <row r="8">
@@ -528,13 +528,13 @@
         <v>60</v>
       </c>
       <c r="B8" t="n">
-        <v>397.0350922179805</v>
+        <v>398.4517852492236</v>
       </c>
       <c r="C8" t="n">
-        <v>825.3543083202798</v>
+        <v>823.4910817089155</v>
       </c>
       <c r="D8" t="n">
-        <v>656.239965458995</v>
+        <v>654.4258338953334</v>
       </c>
     </row>
     <row r="9">
@@ -542,13 +542,13 @@
         <v>65</v>
       </c>
       <c r="B9" t="n">
-        <v>379.3979856054268</v>
+        <v>372.8253540056301</v>
       </c>
       <c r="C9" t="n">
-        <v>932.9747984626913</v>
+        <v>931.1613599221129</v>
       </c>
       <c r="D9" t="n">
-        <v>1005.457023901773</v>
+        <v>994.9288161285315</v>
       </c>
     </row>
     <row r="10">
@@ -556,13 +556,13 @@
         <v>70</v>
       </c>
       <c r="B10" t="n">
-        <v>325.6494752352597</v>
+        <v>324.4951801421341</v>
       </c>
       <c r="C10" t="n">
-        <v>989.6748528158339</v>
+        <v>988.1983678450529</v>
       </c>
       <c r="D10" t="n">
-        <v>1341.45392263164</v>
+        <v>1335.427590763115</v>
       </c>
     </row>
     <row r="11">
@@ -570,13 +570,13 @@
         <v>75</v>
       </c>
       <c r="B11" t="n">
-        <v>267.3840744768929</v>
+        <v>266.5003532530082</v>
       </c>
       <c r="C11" t="n">
-        <v>991.3869797313644</v>
+        <v>988.8606274862764</v>
       </c>
       <c r="D11" t="n">
-        <v>1643.660872689891</v>
+        <v>1641.568252877628</v>
       </c>
     </row>
     <row r="12">
@@ -584,13 +584,13 @@
         <v>80</v>
       </c>
       <c r="B12" t="n">
-        <v>205.4718866429973</v>
+        <v>198.7359174720332</v>
       </c>
       <c r="C12" t="n">
-        <v>932.816019498408</v>
+        <v>936.2966962598333</v>
       </c>
       <c r="D12" t="n">
-        <v>1868.691502717583</v>
+        <v>1866.363327251841</v>
       </c>
     </row>
     <row r="13">
@@ -598,13 +598,13 @@
         <v>85</v>
       </c>
       <c r="B13" t="n">
-        <v>132.4139451995842</v>
+        <v>132.8351969781616</v>
       </c>
       <c r="C13" t="n">
-        <v>822.4027002645677</v>
+        <v>824.8891993891505</v>
       </c>
       <c r="D13" t="n">
-        <v>1984.096132317718</v>
+        <v>1985.683554706425</v>
       </c>
     </row>
     <row r="14">
@@ -612,13 +612,13 @@
         <v>90</v>
       </c>
       <c r="B14" t="n">
-        <v>62.17260080309742</v>
+        <v>78.51212713216802</v>
       </c>
       <c r="C14" t="n">
-        <v>674.5025723399954</v>
+        <v>669.6272767485007</v>
       </c>
       <c r="D14" t="n">
-        <v>1983.882430329726</v>
+        <v>1992.74766794768</v>
       </c>
     </row>
     <row r="15">
@@ -626,13 +626,13 @@
         <v>95</v>
       </c>
       <c r="B15" t="n">
-        <v>23.62025291794367</v>
+        <v>25.92702632423033</v>
       </c>
       <c r="C15" t="n">
-        <v>498.7096043652177</v>
+        <v>494.8993393227161</v>
       </c>
       <c r="D15" t="n">
-        <v>1871.543880786719</v>
+        <v>1867.481904587808</v>
       </c>
     </row>
     <row r="16">
@@ -640,13 +640,13 @@
         <v>100</v>
       </c>
       <c r="B16" t="n">
-        <v>4.002334974620731</v>
+        <v>1.699168191902983</v>
       </c>
       <c r="C16" t="n">
-        <v>338.4877288291863</v>
+        <v>334.7005817627407</v>
       </c>
       <c r="D16" t="n">
-        <v>1640.495898863647</v>
+        <v>1643.832461269614</v>
       </c>
     </row>
   </sheetData>

--- a/monet/tests/TestData/calibrate/pwrmeasured_561nm.xlsx
+++ b/monet/tests/TestData/calibrate/pwrmeasured_561nm.xlsx
@@ -444,13 +444,13 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>131.969111171953</v>
+        <v>131.168460983212</v>
       </c>
       <c r="C2" t="n">
-        <v>5.94018157135772</v>
+        <v>7.868070784901775</v>
       </c>
       <c r="D2" t="n">
-        <v>359.1372415601662</v>
+        <v>352.7730956189264</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>35</v>
       </c>
       <c r="B3" t="n">
-        <v>193.8541630835422</v>
+        <v>197.3719689460794</v>
       </c>
       <c r="C3" t="n">
-        <v>61.99183246980382</v>
+        <v>72.13259654946188</v>
       </c>
       <c r="D3" t="n">
-        <v>135.6314905287634</v>
+        <v>137.6419797826451</v>
       </c>
     </row>
     <row r="4">
@@ -472,13 +472,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="n">
-        <v>265.0945750643727</v>
+        <v>264.8656820236854</v>
       </c>
       <c r="C4" t="n">
-        <v>180.2728142273752</v>
+        <v>176.781226828676</v>
       </c>
       <c r="D4" t="n">
-        <v>15.42443769546204</v>
+        <v>12.54189950748365</v>
       </c>
     </row>
     <row r="5">
@@ -486,13 +486,13 @@
         <v>45</v>
       </c>
       <c r="B5" t="n">
-        <v>325.1442447534625</v>
+        <v>331.5027840334241</v>
       </c>
       <c r="C5" t="n">
-        <v>331.0523127632416</v>
+        <v>333.7155548034026</v>
       </c>
       <c r="D5" t="n">
-        <v>19.9204713420517</v>
+        <v>14.93731810320645</v>
       </c>
     </row>
     <row r="6">
@@ -500,13 +500,13 @@
         <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>373.3555066495359</v>
+        <v>374.3623163277521</v>
       </c>
       <c r="C6" t="n">
-        <v>497.6593583395203</v>
+        <v>506.0646911521113</v>
       </c>
       <c r="D6" t="n">
-        <v>139.8394480500594</v>
+        <v>132.4528490006136</v>
       </c>
     </row>
     <row r="7">
@@ -514,13 +514,13 @@
         <v>55</v>
       </c>
       <c r="B7" t="n">
-        <v>395.3074264806115</v>
+        <v>395.3544007937545</v>
       </c>
       <c r="C7" t="n">
-        <v>672.5777769549796</v>
+        <v>674.1820192080474</v>
       </c>
       <c r="D7" t="n">
-        <v>357.2913190098304</v>
+        <v>360.9721127862035</v>
       </c>
     </row>
     <row r="8">
@@ -528,13 +528,13 @@
         <v>60</v>
       </c>
       <c r="B8" t="n">
-        <v>398.4517852492236</v>
+        <v>396.232288979468</v>
       </c>
       <c r="C8" t="n">
-        <v>823.4910817089155</v>
+        <v>824.4450546268039</v>
       </c>
       <c r="D8" t="n">
-        <v>654.4258338953334</v>
+        <v>662.4576362263866</v>
       </c>
     </row>
     <row r="9">
@@ -542,13 +542,13 @@
         <v>65</v>
       </c>
       <c r="B9" t="n">
-        <v>372.8253540056301</v>
+        <v>376.089187116221</v>
       </c>
       <c r="C9" t="n">
-        <v>931.1613599221129</v>
+        <v>932.8014844869185</v>
       </c>
       <c r="D9" t="n">
-        <v>994.9288161285315</v>
+        <v>1002.601534981018</v>
       </c>
     </row>
     <row r="10">
@@ -556,13 +556,13 @@
         <v>70</v>
       </c>
       <c r="B10" t="n">
-        <v>324.4951801421341</v>
+        <v>335.4478024585227</v>
       </c>
       <c r="C10" t="n">
-        <v>988.1983678450529</v>
+        <v>992.3889137719098</v>
       </c>
       <c r="D10" t="n">
-        <v>1335.427590763115</v>
+        <v>1342.736228545314</v>
       </c>
     </row>
     <row r="11">
@@ -570,13 +570,13 @@
         <v>75</v>
       </c>
       <c r="B11" t="n">
-        <v>266.5003532530082</v>
+        <v>270.2789578426829</v>
       </c>
       <c r="C11" t="n">
-        <v>988.8606274862764</v>
+        <v>992.5358060950683</v>
       </c>
       <c r="D11" t="n">
-        <v>1641.568252877628</v>
+        <v>1637.978793405339</v>
       </c>
     </row>
     <row r="12">
@@ -584,13 +584,13 @@
         <v>80</v>
       </c>
       <c r="B12" t="n">
-        <v>198.7359174720332</v>
+        <v>201.4870997536661</v>
       </c>
       <c r="C12" t="n">
-        <v>936.2966962598333</v>
+        <v>936.6790852955776</v>
       </c>
       <c r="D12" t="n">
-        <v>1866.363327251841</v>
+        <v>1862.900585719746</v>
       </c>
     </row>
     <row r="13">
@@ -598,13 +598,13 @@
         <v>85</v>
       </c>
       <c r="B13" t="n">
-        <v>132.8351969781616</v>
+        <v>127.5911262047183</v>
       </c>
       <c r="C13" t="n">
-        <v>824.8891993891505</v>
+        <v>825.5150206063961</v>
       </c>
       <c r="D13" t="n">
-        <v>1985.683554706425</v>
+        <v>1985.198924924993</v>
       </c>
     </row>
     <row r="14">
@@ -612,13 +612,13 @@
         <v>90</v>
       </c>
       <c r="B14" t="n">
-        <v>78.51212713216802</v>
+        <v>70.07560616835289</v>
       </c>
       <c r="C14" t="n">
-        <v>669.6272767485007</v>
+        <v>674.1417551354953</v>
       </c>
       <c r="D14" t="n">
-        <v>1992.74766794768</v>
+        <v>1983.503611781961</v>
       </c>
     </row>
     <row r="15">
@@ -626,13 +626,13 @@
         <v>95</v>
       </c>
       <c r="B15" t="n">
-        <v>25.92702632423033</v>
+        <v>22.60690110194253</v>
       </c>
       <c r="C15" t="n">
-        <v>494.8993393227161</v>
+        <v>498.6775569085054</v>
       </c>
       <c r="D15" t="n">
-        <v>1867.481904587808</v>
+        <v>1863.594384462552</v>
       </c>
     </row>
     <row r="16">
@@ -640,13 +640,13 @@
         <v>100</v>
       </c>
       <c r="B16" t="n">
-        <v>1.699168191902983</v>
+        <v>-2.958953670913596</v>
       </c>
       <c r="C16" t="n">
-        <v>334.7005817627407</v>
+        <v>326.8300158970304</v>
       </c>
       <c r="D16" t="n">
-        <v>1643.832461269614</v>
+        <v>1638.796928621744</v>
       </c>
     </row>
   </sheetData>
